--- a/data/valuebets_database_2025-09-03.xlsx
+++ b/data/valuebets_database_2025-09-03.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I26"/>
+  <dimension ref="A1:I31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -505,10 +505,8 @@
           <t>04/09 17:00</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>250.00</t>
-        </is>
+      <c r="F2" t="n">
+        <v>250</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -521,7 +519,7 @@
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>45903.06144739113</v>
+        <v>45903.06144739583</v>
       </c>
     </row>
     <row r="3">
@@ -550,10 +548,8 @@
           <t>05/09 16:00</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>200.00</t>
-        </is>
+      <c r="F3" t="n">
+        <v>200</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -566,7 +562,7 @@
         </is>
       </c>
       <c r="I3" s="2" t="n">
-        <v>45903.06144739113</v>
+        <v>45903.06144739583</v>
       </c>
     </row>
     <row r="4">
@@ -595,10 +591,8 @@
           <t>05/09 17:30</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>200.00</t>
-        </is>
+      <c r="F4" t="n">
+        <v>200</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -611,7 +605,7 @@
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>45903.06144739113</v>
+        <v>45903.06144739583</v>
       </c>
     </row>
     <row r="5">
@@ -640,10 +634,8 @@
           <t>04/09 15:00</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>200.00</t>
-        </is>
+      <c r="F5" t="n">
+        <v>200</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -656,7 +648,7 @@
         </is>
       </c>
       <c r="I5" s="2" t="n">
-        <v>45903.06144739113</v>
+        <v>45903.06144739583</v>
       </c>
     </row>
     <row r="6">
@@ -685,10 +677,8 @@
           <t>05/09 17:45</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>175.00</t>
-        </is>
+      <c r="F6" t="n">
+        <v>175</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -701,7 +691,7 @@
         </is>
       </c>
       <c r="I6" s="2" t="n">
-        <v>45903.06144739113</v>
+        <v>45903.06144739583</v>
       </c>
     </row>
     <row r="7">
@@ -730,10 +720,8 @@
           <t>04/09 17:00</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>175.00</t>
-        </is>
+      <c r="F7" t="n">
+        <v>175</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -746,7 +734,7 @@
         </is>
       </c>
       <c r="I7" s="2" t="n">
-        <v>45903.06144739113</v>
+        <v>45903.06144739583</v>
       </c>
     </row>
     <row r="8">
@@ -775,10 +763,8 @@
           <t>05/09 17:45</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>125.00</t>
-        </is>
+      <c r="F8" t="n">
+        <v>125</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -791,7 +777,7 @@
         </is>
       </c>
       <c r="I8" s="2" t="n">
-        <v>45903.06144739113</v>
+        <v>45903.06144739583</v>
       </c>
     </row>
     <row r="9">
@@ -820,10 +806,8 @@
           <t>05/09 17:30</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>140.00</t>
-        </is>
+      <c r="F9" t="n">
+        <v>140</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -836,7 +820,7 @@
         </is>
       </c>
       <c r="I9" s="2" t="n">
-        <v>45903.06144739113</v>
+        <v>45903.06144739583</v>
       </c>
     </row>
     <row r="10">
@@ -865,10 +849,8 @@
           <t>04/09 15:30</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>150.00</t>
-        </is>
+      <c r="F10" t="n">
+        <v>150</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -881,7 +863,7 @@
         </is>
       </c>
       <c r="I10" s="2" t="n">
-        <v>45903.06144739113</v>
+        <v>45903.06144739583</v>
       </c>
     </row>
     <row r="11">
@@ -910,10 +892,8 @@
           <t>04/09 15:30</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>150.00</t>
-        </is>
+      <c r="F11" t="n">
+        <v>150</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -926,7 +906,7 @@
         </is>
       </c>
       <c r="I11" s="2" t="n">
-        <v>45903.06144739113</v>
+        <v>45903.06144739583</v>
       </c>
     </row>
     <row r="12">
@@ -955,10 +935,8 @@
           <t>09/09 15:30</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>125.00</t>
-        </is>
+      <c r="F12" t="n">
+        <v>125</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -971,7 +949,7 @@
         </is>
       </c>
       <c r="I12" s="2" t="n">
-        <v>45903.06144739113</v>
+        <v>45903.06144739583</v>
       </c>
     </row>
     <row r="13">
@@ -1000,10 +978,8 @@
           <t>10/09 16:00</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>125.00</t>
-        </is>
+      <c r="F13" t="n">
+        <v>125</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -1016,7 +992,7 @@
         </is>
       </c>
       <c r="I13" s="2" t="n">
-        <v>45903.06144739113</v>
+        <v>45903.06144739583</v>
       </c>
     </row>
     <row r="14">
@@ -1045,10 +1021,8 @@
           <t>10/09 16:00</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>125.00</t>
-        </is>
+      <c r="F14" t="n">
+        <v>125</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -1061,7 +1035,7 @@
         </is>
       </c>
       <c r="I14" s="2" t="n">
-        <v>45903.06144739113</v>
+        <v>45903.06144739583</v>
       </c>
     </row>
     <row r="15">
@@ -1090,10 +1064,8 @@
           <t>10/09 16:00</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>125.00</t>
-        </is>
+      <c r="F15" t="n">
+        <v>125</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -1106,7 +1078,7 @@
         </is>
       </c>
       <c r="I15" s="2" t="n">
-        <v>45903.06144739113</v>
+        <v>45903.06144739583</v>
       </c>
     </row>
     <row r="16">
@@ -1135,10 +1107,8 @@
           <t>05/09 17:45</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>125.00</t>
-        </is>
+      <c r="F16" t="n">
+        <v>125</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -1151,7 +1121,7 @@
         </is>
       </c>
       <c r="I16" s="2" t="n">
-        <v>45903.06144739113</v>
+        <v>45903.06144739583</v>
       </c>
     </row>
     <row r="17">
@@ -1180,10 +1150,8 @@
           <t>10/09 16:00</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>110.00</t>
-        </is>
+      <c r="F17" t="n">
+        <v>110</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -1196,7 +1164,7 @@
         </is>
       </c>
       <c r="I17" s="2" t="n">
-        <v>45903.06144739113</v>
+        <v>45903.06144739583</v>
       </c>
     </row>
     <row r="18">
@@ -1225,10 +1193,8 @@
           <t>04/09 16:30</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>100.00</t>
-        </is>
+      <c r="F18" t="n">
+        <v>100</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1241,7 +1207,7 @@
         </is>
       </c>
       <c r="I18" s="2" t="n">
-        <v>45903.06144739113</v>
+        <v>45903.06144739583</v>
       </c>
     </row>
     <row r="19">
@@ -1270,10 +1236,8 @@
           <t>07/09 19:00</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>60.00</t>
-        </is>
+      <c r="F19" t="n">
+        <v>60</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1286,7 +1250,7 @@
         </is>
       </c>
       <c r="I19" s="2" t="n">
-        <v>45903.06144739113</v>
+        <v>45903.06144739583</v>
       </c>
     </row>
     <row r="20">
@@ -1315,10 +1279,8 @@
           <t>04/09 00:10</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>75.00</t>
-        </is>
+      <c r="F20" t="n">
+        <v>75</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1331,7 +1293,7 @@
         </is>
       </c>
       <c r="I20" s="2" t="n">
-        <v>45903.06144739113</v>
+        <v>45903.06144739583</v>
       </c>
     </row>
     <row r="21">
@@ -1360,10 +1322,8 @@
           <t>10/09 15:00</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>91.00</t>
-        </is>
+      <c r="F21" t="n">
+        <v>91</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1376,7 +1336,7 @@
         </is>
       </c>
       <c r="I21" s="2" t="n">
-        <v>45903.06144739113</v>
+        <v>45903.06144739583</v>
       </c>
     </row>
     <row r="22">
@@ -1405,10 +1365,8 @@
           <t>05/09 17:45</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>101.00</t>
-        </is>
+      <c r="F22" t="n">
+        <v>101</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1421,7 +1379,7 @@
         </is>
       </c>
       <c r="I22" s="2" t="n">
-        <v>45903.06144739113</v>
+        <v>45903.06144739583</v>
       </c>
     </row>
     <row r="23">
@@ -1450,10 +1408,8 @@
           <t>12/09 22:00</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>60.00</t>
-        </is>
+      <c r="F23" t="n">
+        <v>60</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1466,7 +1422,7 @@
         </is>
       </c>
       <c r="I23" s="2" t="n">
-        <v>45903.06144739113</v>
+        <v>45903.06144739583</v>
       </c>
     </row>
     <row r="24">
@@ -1495,10 +1451,8 @@
           <t>06/09 16:00</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>65.00</t>
-        </is>
+      <c r="F24" t="n">
+        <v>65</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1511,7 +1465,7 @@
         </is>
       </c>
       <c r="I24" s="2" t="n">
-        <v>45903.06144739113</v>
+        <v>45903.06144739583</v>
       </c>
     </row>
     <row r="25">
@@ -1540,10 +1494,8 @@
           <t>06/09 21:30</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F25" t="n">
+        <v>50</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1556,7 +1508,7 @@
         </is>
       </c>
       <c r="I25" s="2" t="n">
-        <v>45903.06144739113</v>
+        <v>45903.06144739583</v>
       </c>
     </row>
     <row r="26">
@@ -1585,10 +1537,8 @@
           <t>06/09 16:00</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>75.00</t>
-        </is>
+      <c r="F26" t="n">
+        <v>75</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1601,7 +1551,232 @@
         </is>
       </c>
       <c r="I26" s="2" t="n">
-        <v>45903.06144739113</v>
+        <v>45903.06144739583</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey | Pas de buts | Lausanne –</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Lausanne – Belfast GiantsEurope - Ligue des Champions</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>05/09 16:00</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>250.00</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>1,41%</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>+251%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="n">
+        <v>45903.12245870565</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey | Pas de buts | Ilves Tamp</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Ilves Tampere – RB SalzbourgLigue des Champions</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>04/09 15:30</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>140.00</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>1,54%</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>+116%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="n">
+        <v>45903.12245870565</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BetClic(FR)Hockey | Pas de buts | Pardubice </t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Pardubice – Mountfield HKRép. Tchèque - Rép. Tchèque Extraliga</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>10/09 16:00</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>125.00</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>1,63%</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>+103%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="n">
+        <v>45903.12245870565</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey | Pas de buts | Sparta Pra</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Sparta Prague – Lulea HFLigue des Champions</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>04/09 16:30</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>110.00</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>1,60%</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>+76,2%</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="n">
+        <v>45903.12245870565</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Moins que 0.5 | Liechtenst</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Liechtenstein – BelgiqueCDM - Qualifs Europe</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Moins que 0.5</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>04/09 18:45</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>85.00</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>1,64%</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>+39,3%</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="n">
+        <v>45903.12245870565</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-09-03.xlsx
+++ b/data/valuebets_database_2025-09-03.xlsx
@@ -1580,10 +1580,8 @@
           <t>05/09 16:00</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>250.00</t>
-        </is>
+      <c r="F27" t="n">
+        <v>250</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -1596,7 +1594,7 @@
         </is>
       </c>
       <c r="I27" s="2" t="n">
-        <v>45903.12245870565</v>
+        <v>45903.12245870371</v>
       </c>
     </row>
     <row r="28">
@@ -1625,10 +1623,8 @@
           <t>04/09 15:30</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>140.00</t>
-        </is>
+      <c r="F28" t="n">
+        <v>140</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -1641,7 +1637,7 @@
         </is>
       </c>
       <c r="I28" s="2" t="n">
-        <v>45903.12245870565</v>
+        <v>45903.12245870371</v>
       </c>
     </row>
     <row r="29">
@@ -1670,10 +1666,8 @@
           <t>10/09 16:00</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>125.00</t>
-        </is>
+      <c r="F29" t="n">
+        <v>125</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -1686,7 +1680,7 @@
         </is>
       </c>
       <c r="I29" s="2" t="n">
-        <v>45903.12245870565</v>
+        <v>45903.12245870371</v>
       </c>
     </row>
     <row r="30">
@@ -1715,10 +1709,8 @@
           <t>04/09 16:30</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>110.00</t>
-        </is>
+      <c r="F30" t="n">
+        <v>110</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -1731,7 +1723,7 @@
         </is>
       </c>
       <c r="I30" s="2" t="n">
-        <v>45903.12245870565</v>
+        <v>45903.12245870371</v>
       </c>
     </row>
     <row r="31">
@@ -1760,10 +1752,8 @@
           <t>04/09 18:45</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>85.00</t>
-        </is>
+      <c r="F31" t="n">
+        <v>85</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -1776,7 +1766,7 @@
         </is>
       </c>
       <c r="I31" s="2" t="n">
-        <v>45903.12245870565</v>
+        <v>45903.12245870371</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-09-03.xlsx
+++ b/data/valuebets_database_2025-09-03.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I31"/>
+  <dimension ref="A1:I32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1769,6 +1769,51 @@
         <v>45903.12245870371</v>
       </c>
     </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey | Pas de buts | KalPa – St</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>KalPa – StorhamarLigue des Champions</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>04/09 15:30</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>140.00</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>1,49%</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>+108%</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="n">
+        <v>45903.18408632436</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/valuebets_database_2025-09-03.xlsx
+++ b/data/valuebets_database_2025-09-03.xlsx
@@ -1795,10 +1795,8 @@
           <t>04/09 15:30</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>140.00</t>
-        </is>
+      <c r="F32" t="n">
+        <v>140</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -1811,7 +1809,7 @@
         </is>
       </c>
       <c r="I32" s="2" t="n">
-        <v>45903.18408632436</v>
+        <v>45903.18408631944</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-09-03.xlsx
+++ b/data/valuebets_database_2025-09-03.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I32"/>
+  <dimension ref="A1:I36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1812,6 +1812,186 @@
         <v>45903.18408631944</v>
       </c>
     </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey | Pas de buts | Eisbären B</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Eisbären Berlin – LukkoEurope - Ligue des Champions</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>05/09 17:30</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>140.00</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>1,46%</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>+105%</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="n">
+        <v>45903.3524446029</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>ParionsSport(FR)Hockey | Pas de buts | Trinec – H</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>ParionsSport(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Trinec – HC OlomoucRép.Tchèque - Extraliga</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>10/09 15:00</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>87.00</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>1,66%</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>+44,0%</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="n">
+        <v>45903.3524446029</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Moins que 0.5 | Finlande –</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Finlande – Saint-MarinEuro (U21) - Qualifs</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Moins que 0.5</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>04/09 14:00</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>55.00</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>2,47%</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>+35,8%</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="n">
+        <v>45903.3524446029</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unibet(FR)Football | Plus que 3.52e équipe | TSC Backa </t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>TSC Backa Topola – Mladost LucaniSuperLiga</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>13/09 08:00</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>50.00</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>2,51%</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>+25,5%</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="n">
+        <v>45903.3524446029</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/valuebets_database_2025-09-03.xlsx
+++ b/data/valuebets_database_2025-09-03.xlsx
@@ -1838,10 +1838,8 @@
           <t>05/09 17:30</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>140.00</t>
-        </is>
+      <c r="F33" t="n">
+        <v>140</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -1854,7 +1852,7 @@
         </is>
       </c>
       <c r="I33" s="2" t="n">
-        <v>45903.3524446029</v>
+        <v>45903.35244460648</v>
       </c>
     </row>
     <row r="34">
@@ -1883,10 +1881,8 @@
           <t>10/09 15:00</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>87.00</t>
-        </is>
+      <c r="F34" t="n">
+        <v>87</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -1899,7 +1895,7 @@
         </is>
       </c>
       <c r="I34" s="2" t="n">
-        <v>45903.3524446029</v>
+        <v>45903.35244460648</v>
       </c>
     </row>
     <row r="35">
@@ -1928,10 +1924,8 @@
           <t>04/09 14:00</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>55.00</t>
-        </is>
+      <c r="F35" t="n">
+        <v>55</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -1944,7 +1938,7 @@
         </is>
       </c>
       <c r="I35" s="2" t="n">
-        <v>45903.3524446029</v>
+        <v>45903.35244460648</v>
       </c>
     </row>
     <row r="36">
@@ -1973,10 +1967,8 @@
           <t>13/09 08:00</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F36" t="n">
+        <v>50</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -1989,7 +1981,7 @@
         </is>
       </c>
       <c r="I36" s="2" t="n">
-        <v>45903.3524446029</v>
+        <v>45903.35244460648</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-09-03.xlsx
+++ b/data/valuebets_database_2025-09-03.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I36"/>
+  <dimension ref="A1:I37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1984,6 +1984,51 @@
         <v>45903.35244460648</v>
       </c>
     </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 2.52e équipe | Etoile Rou</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Etoile Rouge Belgrade – Zeleznicar PancevoSuperLiga</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Plus que 2.52e équipe</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>13/09 08:00</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>45.00</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>2,70%</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>+21,6%</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="n">
+        <v>45903.43131186096</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/valuebets_database_2025-09-03.xlsx
+++ b/data/valuebets_database_2025-09-03.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I37"/>
+  <dimension ref="A1:I38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2010,10 +2010,8 @@
           <t>13/09 08:00</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>45.00</t>
-        </is>
+      <c r="F37" t="n">
+        <v>45</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -2026,7 +2024,52 @@
         </is>
       </c>
       <c r="I37" s="2" t="n">
-        <v>45903.43131186096</v>
+        <v>45903.43131186342</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BetClic(FR)Football | Plus que 2.51re équipe | Bermuda – </t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Bermuda – JamaïqueInternational - Qualif. Am. Nord/Océanie CDM</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Plus que 2.51re équipe</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>05/09 22:00</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>55.00</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>2,42%</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>+32,9%</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="n">
+        <v>45903.47045729304</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-09-03.xlsx
+++ b/data/valuebets_database_2025-09-03.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I38"/>
+  <dimension ref="A1:I41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2053,10 +2053,8 @@
           <t>05/09 22:00</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>55.00</t>
-        </is>
+      <c r="F38" t="n">
+        <v>55</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -2069,7 +2067,142 @@
         </is>
       </c>
       <c r="I38" s="2" t="n">
-        <v>45903.47045729304</v>
+        <v>45903.47045729167</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey | Pas de buts | EV Zug – E</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>EV Zug – ERC IngolstadtLigue des Champions</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>05/09 17:45</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>150.00</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>1,54%</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>+132%</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="n">
+        <v>45903.52917684225</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Bwin(FR)Football | 1 / ANB | Liechtenst</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Bwin(FR)Football</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Liechtenstein – BelgiqueEurope - Éliminatoires CM</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>1 / ANB</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>04/09 18:45</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>4.80</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>31,7%</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>+52,4%</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="n">
+        <v>45903.52917684225</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unibet(FR)Football | Plus que 2.52e équipe | Allemagne </t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Allemagne – Irlande du NordCDM - Qualifs Europe</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Plus que 2.52e équipe</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>07/09 18:45</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>65.00</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>2,10%</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>+36,6%</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="n">
+        <v>45903.52917684225</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-09-03.xlsx
+++ b/data/valuebets_database_2025-09-03.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I41"/>
+  <dimension ref="A1:I44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2096,10 +2096,8 @@
           <t>05/09 17:45</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>150.00</t>
-        </is>
+      <c r="F39" t="n">
+        <v>150</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -2112,7 +2110,7 @@
         </is>
       </c>
       <c r="I39" s="2" t="n">
-        <v>45903.52917684225</v>
+        <v>45903.52917684027</v>
       </c>
     </row>
     <row r="40">
@@ -2141,10 +2139,8 @@
           <t>04/09 18:45</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>4.80</t>
-        </is>
+      <c r="F40" t="n">
+        <v>4.8</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -2157,7 +2153,7 @@
         </is>
       </c>
       <c r="I40" s="2" t="n">
-        <v>45903.52917684225</v>
+        <v>45903.52917684027</v>
       </c>
     </row>
     <row r="41">
@@ -2186,10 +2182,8 @@
           <t>07/09 18:45</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>65.00</t>
-        </is>
+      <c r="F41" t="n">
+        <v>65</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
@@ -2202,7 +2196,142 @@
         </is>
       </c>
       <c r="I41" s="2" t="n">
-        <v>45903.52917684225</v>
+        <v>45903.52917684027</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey | Pas de buts | Ceske Bude</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Ceske Budejovice – Sparta PragueExtraliga</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>09/09 15:30</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>125.00</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>1,65%</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>+106%</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="n">
+        <v>45903.56230076157</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey | Pas de buts | Sparta Pra</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Sparta Prague – Luleå HFEurope - Ligue des Champions</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>04/09 16:30</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>125.00</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>1,42%</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>+77,4%</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="n">
+        <v>45903.56230076157</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Moins que 0.5 | Portugal –</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Portugal – AzerbaïdjanEuro (U21) - Qualifs</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Moins que 0.5</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>05/09 18:30</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>55.00</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>2,38%</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>+30,8%</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="n">
+        <v>45903.56230076157</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-09-03.xlsx
+++ b/data/valuebets_database_2025-09-03.xlsx
@@ -2225,10 +2225,8 @@
           <t>09/09 15:30</t>
         </is>
       </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>125.00</t>
-        </is>
+      <c r="F42" t="n">
+        <v>125</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
@@ -2241,7 +2239,7 @@
         </is>
       </c>
       <c r="I42" s="2" t="n">
-        <v>45903.56230076157</v>
+        <v>45903.56230076389</v>
       </c>
     </row>
     <row r="43">
@@ -2270,10 +2268,8 @@
           <t>04/09 16:30</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>125.00</t>
-        </is>
+      <c r="F43" t="n">
+        <v>125</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
@@ -2286,7 +2282,7 @@
         </is>
       </c>
       <c r="I43" s="2" t="n">
-        <v>45903.56230076157</v>
+        <v>45903.56230076389</v>
       </c>
     </row>
     <row r="44">
@@ -2315,10 +2311,8 @@
           <t>05/09 18:30</t>
         </is>
       </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>55.00</t>
-        </is>
+      <c r="F44" t="n">
+        <v>55</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
@@ -2331,7 +2325,7 @@
         </is>
       </c>
       <c r="I44" s="2" t="n">
-        <v>45903.56230076157</v>
+        <v>45903.56230076389</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-09-03.xlsx
+++ b/data/valuebets_database_2025-09-03.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I44"/>
+  <dimension ref="A1:I45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2328,6 +2328,51 @@
         <v>45903.56230076389</v>
       </c>
     </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unibet(FR)Football | Plus que 3.52e équipe | Deportivo </t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Deportivo Riestra – Central CordobaLiga Profesional</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>12/09 17:30</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>60.00</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>2,32%</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>+39,3%</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="n">
+        <v>45903.64079545191</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/valuebets_database_2025-09-03.xlsx
+++ b/data/valuebets_database_2025-09-03.xlsx
@@ -2354,10 +2354,8 @@
           <t>12/09 17:30</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>60.00</t>
-        </is>
+      <c r="F45" t="n">
+        <v>60</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
@@ -2370,7 +2368,7 @@
         </is>
       </c>
       <c r="I45" s="2" t="n">
-        <v>45903.64079545191</v>
+        <v>45903.64079545139</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-09-03.xlsx
+++ b/data/valuebets_database_2025-09-03.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I45"/>
+  <dimension ref="A1:I46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2371,6 +2371,51 @@
         <v>45903.64079545139</v>
       </c>
     </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | Samsunspor</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Samsunspor – AntalyasporSüper Lig</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>13/09 14:00</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>60.00</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>2,43%</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>+46,0%</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="n">
+        <v>45903.72078341868</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/valuebets_database_2025-09-03.xlsx
+++ b/data/valuebets_database_2025-09-03.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I46"/>
+  <dimension ref="A1:I47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2397,10 +2397,8 @@
           <t>13/09 14:00</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>60.00</t>
-        </is>
+      <c r="F46" t="n">
+        <v>60</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
@@ -2413,7 +2411,52 @@
         </is>
       </c>
       <c r="I46" s="2" t="n">
-        <v>45903.72078341868</v>
+        <v>45903.72078341435</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BetClic(FR)Hockey | Pas de buts | Bolzano – </t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Bolzano – Kometa BrnoEurope - Ligue des Champions</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>05/09 17:45</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>125.00</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>1,47%</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>+84,1%</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="n">
+        <v>45903.77050463491</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-09-03.xlsx
+++ b/data/valuebets_database_2025-09-03.xlsx
@@ -2440,10 +2440,8 @@
           <t>05/09 17:45</t>
         </is>
       </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>125.00</t>
-        </is>
+      <c r="F47" t="n">
+        <v>125</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
@@ -2456,7 +2454,7 @@
         </is>
       </c>
       <c r="I47" s="2" t="n">
-        <v>45903.77050463491</v>
+        <v>45903.77050462963</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-09-03.xlsx
+++ b/data/valuebets_database_2025-09-03.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I47"/>
+  <dimension ref="A1:I48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2457,6 +2457,51 @@
         <v>45903.77050462963</v>
       </c>
     </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 2.52e équipe | France – I</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>France – IslandeCDM - Qualifs Europe</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Plus que 2.52e équipe</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>09/09 18:45</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>55.00</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>2,38%</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>+31,1%</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="n">
+        <v>45903.97107975057</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
